--- a/_extract_osv/Svod_finansovye_pokazateli_2024.xlsx
+++ b/_extract_osv/Svod_finansovye_pokazateli_2024.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="40">
   <si>
     <t>2024год</t>
   </si>
@@ -123,6 +123,18 @@
   </si>
   <si>
     <t>в отчет за год</t>
+  </si>
+  <si>
+    <t>сч02</t>
+  </si>
+  <si>
+    <t>амортизация а/маш</t>
+  </si>
+  <si>
+    <t>администр. расх</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сч02 </t>
   </si>
 </sst>
 </file>
@@ -194,7 +206,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -207,8 +219,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -216,11 +234,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFACC8BD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFACC8BD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFACC8BD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFACC8BD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -234,9 +267,6 @@
     <xf numFmtId="17" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -252,16 +282,65 @@
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -567,237 +646,280 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:J34"/>
+  <dimension ref="A2:J36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="25.140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="19.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" style="10" customWidth="1"/>
     <col min="6" max="8" width="9.140625" style="2"/>
     <col min="9" max="9" width="13" style="2" customWidth="1"/>
     <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="D3" s="12"/>
+      <c r="E3" s="13"/>
+    </row>
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="14" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E4" s="13"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="12">
         <v>149500</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="12">
         <v>10382200</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="12">
         <v>2241939.34</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E7" s="13"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="12">
         <v>579300</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E8" s="13"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="12">
         <v>28500</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="E9" s="13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="14">
         <f>SUM(D5:D9)</f>
         <v>13381439.34</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="15">
         <v>10382200</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="E11" s="13"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
+    </row>
+    <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="14">
-        <v>7728909.9500000002</v>
-      </c>
-      <c r="E14" s="15">
-        <f>D14</f>
-        <v>7728909.9500000002</v>
+      <c r="D14" s="21">
+        <v>5851654.3700000001</v>
+      </c>
+      <c r="E14" s="22">
+        <v>5297737.8</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="21"/>
+      <c r="E15" s="13">
+        <v>458333.36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.25">
+      <c r="C16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="21"/>
+      <c r="E16" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D17" s="23">
         <v>5264825.33</v>
       </c>
-      <c r="E15">
+      <c r="E17" s="24">
         <v>2342950.2599999998</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
+    <row r="18" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D18" s="23">
         <v>1429663.43</v>
       </c>
-      <c r="E16">
+      <c r="E18" s="24">
         <v>1336238.43</v>
       </c>
-      <c r="I16" s="7"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C17" s="2" t="s">
+      <c r="I18" s="6"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="7">
-        <f>D16+D15</f>
+      <c r="D19" s="6">
+        <f>D18+D17</f>
         <v>6694488.7599999998</v>
       </c>
-      <c r="E17" s="2">
-        <f>E16+E15</f>
+      <c r="E19" s="13">
+        <f>E18+E17</f>
         <v>3679188.6899999995</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="8">
-        <f>D17*0.13</f>
+      <c r="D20" s="16">
+        <f>D19*0.13</f>
         <v>870283.53879999998</v>
       </c>
-      <c r="E18" s="2">
-        <f>E17*0.13</f>
+      <c r="E20" s="13">
+        <f>E19*0.13</f>
         <v>478294.52969999996</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="18" x14ac:dyDescent="0.25">
-      <c r="C19" s="3" t="s">
+    <row r="21" spans="2:10" ht="18" x14ac:dyDescent="0.25">
+      <c r="C21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="11">
-        <f>D18+D17+D14</f>
-        <v>15293682.2488</v>
-      </c>
-      <c r="E19" s="11">
-        <f>E18+E17+E14</f>
-        <v>11886393.1697</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="C22" s="2" t="s">
+      <c r="D21" s="17">
+        <f>D20+D19+D14</f>
+        <v>13416426.6688</v>
+      </c>
+      <c r="E21" s="18">
+        <f>E20+E19+E14+E15</f>
+        <v>9913554.3796999976</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="D22" s="12"/>
+      <c r="E22" s="13"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="D23" s="12"/>
+      <c r="E23" s="13"/>
+    </row>
+    <row r="24" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+      <c r="C24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="6">
-        <f>D11-D19</f>
-        <v>-4911482.2488000002</v>
-      </c>
-      <c r="E22" s="5">
-        <f>D11-E19</f>
-        <v>-1504193.1697000004</v>
-      </c>
-    </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E34" s="2" t="s">
+      <c r="D24" s="19">
+        <f>D11-D21</f>
+        <v>-3034226.6688000001</v>
+      </c>
+      <c r="E24" s="20">
+        <f>D11-E21</f>
+        <v>468645.6203000024</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I25" s="11">
+        <v>458333.36</v>
+      </c>
+    </row>
+    <row r="36" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E36" s="10" t="s">
         <v>6</v>
       </c>
     </row>
@@ -809,30 +931,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:J34"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:J35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="25.140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="19.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.5703125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" style="13" customWidth="1"/>
     <col min="6" max="8" width="9.140625" style="2"/>
     <col min="9" max="9" width="13" style="2" customWidth="1"/>
     <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
         <v>3</v>
@@ -841,7 +963,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
@@ -849,13 +971,13 @@
         <v>32</v>
       </c>
       <c r="D5" s="2">
-        <v>14329200</v>
-      </c>
-      <c r="E5" s="2" t="s">
+        <v>1432900</v>
+      </c>
+      <c r="E5" s="13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
@@ -865,11 +987,11 @@
       <c r="D6" s="2">
         <v>6780694.7999999998</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
@@ -877,13 +999,13 @@
         <v>10</v>
       </c>
       <c r="D7" s="2">
-        <v>214211.77</v>
-      </c>
-      <c r="E7" s="2" t="s">
+        <v>314211.77</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
@@ -894,7 +1016,7 @@
         <v>1733553.5</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
@@ -902,35 +1024,35 @@
         <v>485400</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D10" s="3">
         <f>SUM(D5:D9)</f>
-        <v>23543060.07</v>
-      </c>
-      <c r="E10" s="2" t="s">
+        <v>10746760.07</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="18" x14ac:dyDescent="0.2">
       <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <f>D6</f>
         <v>6780694.7999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="13" t="s">
         <v>27</v>
       </c>
       <c r="I13" s="2" t="s">
@@ -944,130 +1066,142 @@
       <c r="C14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="12">
-        <v>108014610.75</v>
-      </c>
-      <c r="E14" s="12">
-        <v>108014610.75</v>
+      <c r="D14" s="25">
+        <v>4836532</v>
+      </c>
+      <c r="E14" s="24">
+        <v>5817462.9800000004</v>
       </c>
       <c r="I14" s="2">
         <f>D14</f>
-        <v>108014610.75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>4836532</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="25"/>
+      <c r="E15" s="27">
+        <v>499999.98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D16" s="26">
         <v>5052470.5999999996</v>
       </c>
-      <c r="E15" s="13">
-        <v>2085647.83</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="E16" s="28">
+        <v>2105678.5499999998</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I16" s="2">
         <v>3629342.14</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
+    <row r="17" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D17" s="26">
         <v>1412117.37</v>
       </c>
-      <c r="E16">
+      <c r="E17" s="24">
         <v>1360897.5</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I17" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C17" s="2" t="s">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="C18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="7">
-        <f>D16+D15</f>
+      <c r="D18" s="6">
+        <f>D17+D16</f>
         <v>6464587.9699999997</v>
       </c>
-      <c r="E17" s="2">
-        <f>E16+E15</f>
-        <v>3446545.33</v>
-      </c>
-      <c r="I17" s="2">
+      <c r="E18" s="13">
+        <f>E17+E16</f>
+        <v>3466576.05</v>
+      </c>
+      <c r="I18" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="8">
-        <f>D17*0.13</f>
+      <c r="D19" s="7">
+        <f>D18*0.13</f>
         <v>840396.43610000005</v>
       </c>
-      <c r="E18" s="5">
-        <f>E17*0.13</f>
-        <v>448050.89290000004</v>
-      </c>
-      <c r="I18" s="2">
+      <c r="E19" s="20">
+        <f>E18*0.13</f>
+        <v>450654.88649999996</v>
+      </c>
+      <c r="I19" s="2">
         <v>729931.11</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C19" s="3" t="s">
+    <row r="20" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="10">
-        <f>D18+D17+D14</f>
-        <v>115319595.1561</v>
-      </c>
-      <c r="E19" s="10">
-        <f>E18+E17+E14</f>
-        <v>111909206.9729</v>
-      </c>
-      <c r="I19" s="2">
-        <f>SUM(I14:I18)</f>
-        <v>112373884</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="I21" s="2">
-        <f>D11-I19</f>
-        <v>-105593189.2</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="C22" s="2" t="s">
+      <c r="D20" s="9">
+        <f>D19+D18+D14</f>
+        <v>12141516.406099999</v>
+      </c>
+      <c r="E20" s="29">
+        <f>E19+E18+E14+E15</f>
+        <v>10234693.896500001</v>
+      </c>
+      <c r="I20" s="2">
+        <f>SUM(I14:I19)</f>
+        <v>9195805.25</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I22" s="2">
+        <f>D11-I20</f>
+        <v>-2415110.4500000002</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="15" x14ac:dyDescent="0.2">
+      <c r="C23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="6">
-        <f>D11-D19</f>
-        <v>-108538900.35610001</v>
-      </c>
-      <c r="E22" s="5">
-        <f>D11-E19</f>
-        <v>-105128512.17290001</v>
-      </c>
-    </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E34" s="2" t="s">
+      <c r="D23" s="5">
+        <f>D11-D20</f>
+        <v>-5360821.6060999995</v>
+      </c>
+      <c r="E23" s="20">
+        <f>D11-E20</f>
+        <v>-3453999.0965000009</v>
+      </c>
+    </row>
+    <row r="35" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E35" s="13" t="s">
         <v>6</v>
       </c>
     </row>
